--- a/問い合わせ対応削減.xlsx
+++ b/問い合わせ対応削減.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\canon\OneDrive\デスクトップ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36134743-D97B-4371-864C-294FB61982C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777C793D-1242-4A57-BDAA-E0897C7AAA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{639A3C99-A6E4-4507-BC46-FFF3C822E640}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>提案</t>
     <rPh sb="0" eb="2">
@@ -443,12 +443,38 @@
     <t>※「人間が介在しなくても流れるはずの情報に、人間が張り付いている状態」</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>※メーリスに応じてPAでListsに転記</t>
+    <rPh sb="6" eb="7">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※Listsに回答を記入するとPAでメール自動作成・送信</t>
+    <rPh sb="7" eb="9">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ジドウサクセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +518,20 @@
     <font>
       <sz val="11"/>
       <color theme="2" tint="-0.499984740745262"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -541,7 +581,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -561,6 +601,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -685,13 +731,13 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>752379</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>133349</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>346628</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -721,8 +767,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9077229" y="1533525"/>
-          <a:ext cx="4019645" cy="2628900"/>
+          <a:off x="9077229" y="1533524"/>
+          <a:ext cx="6976124" cy="4562476"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1194,6 +1240,9 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
       </c>
@@ -1205,6 +1254,9 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A25" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="I25" s="3" t="s">
         <v>23</v>
       </c>
